--- a/tests/fixtures/inventarios/inventario_reactivos_pruebas.xlsx
+++ b/tests/fixtures/inventarios/inventario_reactivos_pruebas.xlsx
@@ -4,7 +4,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Inventario" sheetId="1" r:id="rId1"/>
+    <sheet name="Casos de prueba" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Inventario!$A$1:$P$33</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -397,17 +401,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:P33"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,595 +444,2049 @@
         <v>MARCA</v>
       </c>
       <c r="H1" t="str">
+        <v>MODELO</v>
+      </c>
+      <c r="I1" t="str">
         <v>PROVEEDOR</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>OBSERVACIONES</v>
+      </c>
+      <c r="K1" t="str">
+        <v>CÓDIGO INTERNO</v>
+      </c>
+      <c r="L1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="M1" t="str">
+        <v>CÓDIGO DE BARRAS</v>
+      </c>
+      <c r="N1" t="str">
+        <v>QR</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PLACA LOCAL</v>
+      </c>
+      <c r="P1" t="str">
+        <v>ETIQUETADO</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>REF-QA-001-5648</v>
+        <v>REAC-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Reactivo QA Patrón de calibración sintético 1</v>
+        <v>Cloruro de sodio</v>
       </c>
       <c r="C2" t="str">
-        <v>267.1 g</v>
+        <v>1250 g</v>
       </c>
       <c r="D2" t="str">
-        <v>446.0 g</v>
+        <v>2.5 kg</v>
       </c>
       <c r="E2" t="str">
-        <v>148.4 g</v>
+        <v>100 g</v>
       </c>
       <c r="F2" t="str">
-        <v>104.8 g</v>
+        <v>0.5 kg</v>
       </c>
       <c r="G2" t="str">
-        <v>Marca QA Norte</v>
+        <v>Genérica</v>
       </c>
       <c r="H2" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>QR-REAC-001</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>REF-QA-002-8054</v>
+        <v>REAC-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Reactivo QA Solución tampón de prueba 2</v>
+        <v>Agua destilada</v>
       </c>
       <c r="C3" t="str">
-        <v>440.7 ml</v>
+        <v>0 ml</v>
       </c>
       <c r="D3" t="str">
-        <v>470.3 ml</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>349.4 ml</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>225.7 ml</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Marca QA Sur</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>REF-QA-003-6853</v>
+        <v>REAC-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Reactivo QA Solución demostrativa simulada 3</v>
+        <v>Cloruro de potasio</v>
       </c>
       <c r="C4" t="str">
-        <v>158.2 g</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>171.9 g</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>287.9 g</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>483.4 g</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>REF-QA-004-5678</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>Reactivo QA Solución demostrativa simulada 4</v>
+        <v>Carbonato de calcio</v>
       </c>
       <c r="C5" t="str">
-        <v>81.7 ml</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>422.7 ml</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>76.6 ml</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>124.4 ml</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>REF-QA-005-4170</v>
+        <v>REAC-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Reactivo QA Material reactivo ficticio 5</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>347.1 g</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>192.6 g</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>107.7 g</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>20.0 g</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>REF-QA-006-7484</v>
+        <v>REAC-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Reactivo QA Material reactivo ficticio 6</v>
+        <v>Solución patrón</v>
       </c>
       <c r="C7" t="str">
-        <v>122.9 ml</v>
+        <v>dos gramos</v>
       </c>
       <c r="D7" t="str">
-        <v>307.0 ml</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>435.9 ml</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>322.0 ml</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>REF-QA-007-5671</v>
+        <v>REAC-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Reactivo QA Reactivo experimental QA 7</v>
+        <v>Etanol</v>
       </c>
       <c r="C8" t="str">
-        <v>7.3 g</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>262.4 g</v>
+        <v>500</v>
       </c>
       <c r="E8" t="str">
-        <v>459.0 g</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>231.0 g</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>REF-QA-008-4015</v>
+        <v>REAC-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Reactivo QA Reactivo de referencia sintético 8</v>
+        <v>Acetona</v>
       </c>
       <c r="C9" t="str">
-        <v>277.8 ml</v>
+        <v>-1 g</v>
       </c>
       <c r="D9" t="str">
-        <v>214.6 ml</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>398.4 ml</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>301.8 ml</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>REF-QA-009-5487</v>
+        <v>REAC-009</v>
       </c>
       <c r="B10" t="str">
-        <v>Reactivo QA Material reactivo ficticio 9</v>
+        <v>Sacarosa</v>
       </c>
       <c r="C10" t="str">
-        <v>266.0 g</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>337.6 g</v>
+        <v>1.2345 g</v>
       </c>
       <c r="E10" t="str">
-        <v>145.3 g</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>429.3 g</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>REF-QA-010-4487</v>
+        <v>REAC-010</v>
       </c>
       <c r="B11" t="str">
-        <v>Reactivo QA Muestra de referencia ficticia 10</v>
+        <v>Glucosa</v>
       </c>
       <c r="C11" t="str">
-        <v>43.4 ml</v>
+        <v>100000000000 g</v>
       </c>
       <c r="D11" t="str">
-        <v>421.5 ml</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>191.3 ml</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>466.7 ml</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>REF-QA-011-5584</v>
+        <v>REAC-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Reactivo QA Reactivo experimental QA 11</v>
+        <v>Reactivo con unidad extensa</v>
       </c>
       <c r="C12" t="str">
-        <v>285.3 g</v>
+        <v>1 ggggggggggggggggggggggggggggggggggggggggggggggggggg</v>
       </c>
       <c r="D12" t="str">
-        <v>356.7 g</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>203.0 g</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>108.7 g</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>REF-QA-012-1563</v>
+        <v>RRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRRR</v>
       </c>
       <c r="B13" t="str">
-        <v>Reactivo QA Solución tampón de prueba 12</v>
+        <v>Reactivo con referencia extensa</v>
       </c>
       <c r="C13" t="str">
-        <v>152.5 ml</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>36.5 ml</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>241.5 ml</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>472.4 ml</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Marca QA Sur</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>REF-QA-013-4233</v>
+        <v>REAC-013</v>
       </c>
       <c r="B14" t="str">
-        <v>Reactivo QA Patrón de calibración sintético 13</v>
+        <v>DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD</v>
       </c>
       <c r="C14" t="str">
-        <v>164.3 g</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>6.4 g</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>57.2 g</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>210.8 g</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>REF-QA-014-8497</v>
+        <v>REAC-014</v>
       </c>
       <c r="B15" t="str">
-        <v>Reactivo QA Solución tampón de prueba 14</v>
+        <v>Reactivo con QR repetido</v>
       </c>
       <c r="C15" t="str">
-        <v>394.2 ml</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>296.9 ml</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>296.9 ml</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>343.2 ml</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>QR-REAC-001</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>REF-QA-015-7921</v>
+        <v>REAC-015</v>
       </c>
       <c r="B16" t="str">
-        <v>Reactivo QA Material reactivo ficticio 15</v>
+        <v>Reactivo con observación extensa</v>
       </c>
       <c r="C16" t="str">
-        <v>87.5 g</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>441.7 g</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>70.7 g</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>32.0 g</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>OOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOO</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>REF-QA-016-6171</v>
+        <v>REAC-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Reactivo QA Indicador de prueba QA 16</v>
+        <v>Bicarbonato de sodio</v>
       </c>
       <c r="C17" t="str">
-        <v>116.4 ml</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>217.2 ml</v>
+        <v>250 g</v>
       </c>
       <c r="E17" t="str">
-        <v>431.2 ml</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>330.4 ml</v>
+        <v>25 g</v>
       </c>
       <c r="G17" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>REF-QA-017-1527</v>
+        <v>REAC-017</v>
       </c>
       <c r="B18" t="str">
-        <v>Reactivo QA Patrón de calibración sintético 17</v>
+        <v>Solución amortiguadora</v>
       </c>
       <c r="C18" t="str">
-        <v>242.8 g</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v>79.2 g</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>104.6 g</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>497.9 g</v>
+        <v>0 ml</v>
       </c>
       <c r="G18" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>REF-QA-018-6924</v>
+        <v>REAC-ADIC-001</v>
       </c>
       <c r="B19" t="str">
-        <v>Reactivo QA Solución tampón de prueba 18</v>
+        <v>Reactivo de laboratorio de prueba 001</v>
       </c>
       <c r="C19" t="str">
-        <v>51.1 ml</v>
+        <v>1 g</v>
       </c>
       <c r="D19" t="str">
-        <v>146.3 ml</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>480.6 ml</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>96.5 ml</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>Marca QA Centro</v>
+        <v>Marca Demo</v>
       </c>
       <c r="H19" t="str">
-        <v>Proveedor de pruebas</v>
+        <v>RD-001</v>
       </c>
       <c r="I19" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Caso exitoso adicional 001.</v>
+      </c>
+      <c r="K19" t="str">
+        <v>INT-REAC-ADIC-001</v>
+      </c>
+      <c r="L19" t="str">
+        <v>ID-REAC-ADIC-001</v>
+      </c>
+      <c r="M19" t="str">
+        <v>BAR-REAC-ADIC-001</v>
+      </c>
+      <c r="N19" t="str">
+        <v>QR-REAC-ADIC-001</v>
+      </c>
+      <c r="O19" t="str">
+        <v>LOC-REAC-ADIC-001</v>
+      </c>
+      <c r="P19" t="str">
+        <v>TAG-REAC-ADIC-001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>REF-QA-019-9580</v>
+        <v>REAC-ADIC-002</v>
       </c>
       <c r="B20" t="str">
-        <v>Reactivo QA Reactivo experimental QA 19</v>
+        <v>Reactivo de laboratorio de prueba 002</v>
       </c>
       <c r="C20" t="str">
-        <v>360.1 g</v>
+        <v>2 g</v>
       </c>
       <c r="D20" t="str">
-        <v>76.8 g</v>
+        <v>2,5 g</v>
       </c>
       <c r="E20" t="str">
-        <v>493.4 g</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>108.6 g</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>Marca QA Sur</v>
+        <v>Marca Demo</v>
       </c>
       <c r="H20" t="str">
-        <v>Proveedor de pruebas</v>
+        <v>RD-002</v>
       </c>
       <c r="I20" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Caso exitoso adicional 002.</v>
+      </c>
+      <c r="K20" t="str">
+        <v>INT-REAC-ADIC-002</v>
+      </c>
+      <c r="L20" t="str">
+        <v>ID-REAC-ADIC-002</v>
+      </c>
+      <c r="M20" t="str">
+        <v>BAR-REAC-ADIC-002</v>
+      </c>
+      <c r="N20" t="str">
+        <v>QR-REAC-ADIC-002</v>
+      </c>
+      <c r="O20" t="str">
+        <v>LOC-REAC-ADIC-002</v>
+      </c>
+      <c r="P20" t="str">
+        <v>TAG-REAC-ADIC-002</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>REF-QA-020-8570</v>
+        <v>REAC-ADIC-003</v>
       </c>
       <c r="B21" t="str">
-        <v>Reactivo QA Muestra de referencia ficticia 20</v>
+        <v>Reactivo de laboratorio de prueba 003</v>
       </c>
       <c r="C21" t="str">
-        <v>247.4 ml</v>
+        <v>3 g</v>
       </c>
       <c r="D21" t="str">
-        <v>184.8 ml</v>
+        <v/>
       </c>
       <c r="E21" t="str">
-        <v>15.6 ml</v>
+        <v>1 ml</v>
       </c>
       <c r="F21" t="str">
-        <v>407.5 ml</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>Marca de prueba Uno</v>
+        <v>Marca Demo</v>
       </c>
       <c r="H21" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v>RD-003</v>
       </c>
       <c r="I21" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Caso exitoso adicional 003.</v>
+      </c>
+      <c r="K21" t="str">
+        <v>INT-REAC-ADIC-003</v>
+      </c>
+      <c r="L21" t="str">
+        <v>ID-REAC-ADIC-003</v>
+      </c>
+      <c r="M21" t="str">
+        <v>BAR-REAC-ADIC-003</v>
+      </c>
+      <c r="N21" t="str">
+        <v>QR-REAC-ADIC-003</v>
+      </c>
+      <c r="O21" t="str">
+        <v>LOC-REAC-ADIC-003</v>
+      </c>
+      <c r="P21" t="str">
+        <v>TAG-REAC-ADIC-003</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>REAC-ADIC-004</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Reactivo de laboratorio de prueba 004</v>
+      </c>
+      <c r="C22" t="str">
+        <v>4 g</v>
+      </c>
+      <c r="D22" t="str">
+        <v>4,5 g</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>0,5 ml</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H22" t="str">
+        <v>RD-004</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Caso exitoso adicional 004.</v>
+      </c>
+      <c r="K22" t="str">
+        <v>INT-REAC-ADIC-004</v>
+      </c>
+      <c r="L22" t="str">
+        <v>ID-REAC-ADIC-004</v>
+      </c>
+      <c r="M22" t="str">
+        <v>BAR-REAC-ADIC-004</v>
+      </c>
+      <c r="N22" t="str">
+        <v>QR-REAC-ADIC-004</v>
+      </c>
+      <c r="O22" t="str">
+        <v>LOC-REAC-ADIC-004</v>
+      </c>
+      <c r="P22" t="str">
+        <v>TAG-REAC-ADIC-004</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>REAC-ADIC-005</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Reactivo de laboratorio de prueba 005</v>
+      </c>
+      <c r="C23" t="str">
+        <v>5 g</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H23" t="str">
+        <v>RD-005</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Caso exitoso adicional 005.</v>
+      </c>
+      <c r="K23" t="str">
+        <v>INT-REAC-ADIC-005</v>
+      </c>
+      <c r="L23" t="str">
+        <v>ID-REAC-ADIC-005</v>
+      </c>
+      <c r="M23" t="str">
+        <v>BAR-REAC-ADIC-005</v>
+      </c>
+      <c r="N23" t="str">
+        <v>QR-REAC-ADIC-005</v>
+      </c>
+      <c r="O23" t="str">
+        <v>LOC-REAC-ADIC-005</v>
+      </c>
+      <c r="P23" t="str">
+        <v>TAG-REAC-ADIC-005</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>REAC-ADIC-006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Reactivo de laboratorio de prueba 006</v>
+      </c>
+      <c r="C24" t="str">
+        <v>6 g</v>
+      </c>
+      <c r="D24" t="str">
+        <v>6,5 g</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1 ml</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H24" t="str">
+        <v>RD-006</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Caso exitoso adicional 006.</v>
+      </c>
+      <c r="K24" t="str">
+        <v>INT-REAC-ADIC-006</v>
+      </c>
+      <c r="L24" t="str">
+        <v>ID-REAC-ADIC-006</v>
+      </c>
+      <c r="M24" t="str">
+        <v>BAR-REAC-ADIC-006</v>
+      </c>
+      <c r="N24" t="str">
+        <v>QR-REAC-ADIC-006</v>
+      </c>
+      <c r="O24" t="str">
+        <v>LOC-REAC-ADIC-006</v>
+      </c>
+      <c r="P24" t="str">
+        <v>TAG-REAC-ADIC-006</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>REAC-ADIC-007</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Reactivo de laboratorio de prueba 007</v>
+      </c>
+      <c r="C25" t="str">
+        <v>7 g</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H25" t="str">
+        <v>RD-007</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Caso exitoso adicional 007.</v>
+      </c>
+      <c r="K25" t="str">
+        <v>INT-REAC-ADIC-007</v>
+      </c>
+      <c r="L25" t="str">
+        <v>ID-REAC-ADIC-007</v>
+      </c>
+      <c r="M25" t="str">
+        <v>BAR-REAC-ADIC-007</v>
+      </c>
+      <c r="N25" t="str">
+        <v>QR-REAC-ADIC-007</v>
+      </c>
+      <c r="O25" t="str">
+        <v>LOC-REAC-ADIC-007</v>
+      </c>
+      <c r="P25" t="str">
+        <v>TAG-REAC-ADIC-007</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>REAC-ADIC-008</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Reactivo de laboratorio de prueba 008</v>
+      </c>
+      <c r="C26" t="str">
+        <v>8 g</v>
+      </c>
+      <c r="D26" t="str">
+        <v>8,5 g</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>0,5 ml</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H26" t="str">
+        <v>RD-008</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Caso exitoso adicional 008.</v>
+      </c>
+      <c r="K26" t="str">
+        <v>INT-REAC-ADIC-008</v>
+      </c>
+      <c r="L26" t="str">
+        <v>ID-REAC-ADIC-008</v>
+      </c>
+      <c r="M26" t="str">
+        <v>BAR-REAC-ADIC-008</v>
+      </c>
+      <c r="N26" t="str">
+        <v>QR-REAC-ADIC-008</v>
+      </c>
+      <c r="O26" t="str">
+        <v>LOC-REAC-ADIC-008</v>
+      </c>
+      <c r="P26" t="str">
+        <v>TAG-REAC-ADIC-008</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>REAC-ADIC-009</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Reactivo de laboratorio de prueba 009</v>
+      </c>
+      <c r="C27" t="str">
+        <v>9 g</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>1 ml</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H27" t="str">
+        <v>RD-009</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Caso exitoso adicional 009.</v>
+      </c>
+      <c r="K27" t="str">
+        <v>INT-REAC-ADIC-009</v>
+      </c>
+      <c r="L27" t="str">
+        <v>ID-REAC-ADIC-009</v>
+      </c>
+      <c r="M27" t="str">
+        <v>BAR-REAC-ADIC-009</v>
+      </c>
+      <c r="N27" t="str">
+        <v>QR-REAC-ADIC-009</v>
+      </c>
+      <c r="O27" t="str">
+        <v>LOC-REAC-ADIC-009</v>
+      </c>
+      <c r="P27" t="str">
+        <v>TAG-REAC-ADIC-009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>REAC-ADIC-010</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Reactivo de laboratorio de prueba 010</v>
+      </c>
+      <c r="C28" t="str">
+        <v>10 g</v>
+      </c>
+      <c r="D28" t="str">
+        <v>10,5 g</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H28" t="str">
+        <v>RD-010</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Caso exitoso adicional 010.</v>
+      </c>
+      <c r="K28" t="str">
+        <v>INT-REAC-ADIC-010</v>
+      </c>
+      <c r="L28" t="str">
+        <v>ID-REAC-ADIC-010</v>
+      </c>
+      <c r="M28" t="str">
+        <v>BAR-REAC-ADIC-010</v>
+      </c>
+      <c r="N28" t="str">
+        <v>QR-REAC-ADIC-010</v>
+      </c>
+      <c r="O28" t="str">
+        <v>LOC-REAC-ADIC-010</v>
+      </c>
+      <c r="P28" t="str">
+        <v>TAG-REAC-ADIC-010</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>REAC-ADIC-011</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Reactivo de laboratorio de prueba 011</v>
+      </c>
+      <c r="C29" t="str">
+        <v>11 g</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H29" t="str">
+        <v>RD-011</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Caso exitoso adicional 011.</v>
+      </c>
+      <c r="K29" t="str">
+        <v>INT-REAC-ADIC-011</v>
+      </c>
+      <c r="L29" t="str">
+        <v>ID-REAC-ADIC-011</v>
+      </c>
+      <c r="M29" t="str">
+        <v>BAR-REAC-ADIC-011</v>
+      </c>
+      <c r="N29" t="str">
+        <v>QR-REAC-ADIC-011</v>
+      </c>
+      <c r="O29" t="str">
+        <v>LOC-REAC-ADIC-011</v>
+      </c>
+      <c r="P29" t="str">
+        <v>TAG-REAC-ADIC-011</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>REAC-ADIC-012</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Reactivo de laboratorio de prueba 012</v>
+      </c>
+      <c r="C30" t="str">
+        <v>12 g</v>
+      </c>
+      <c r="D30" t="str">
+        <v>12,5 g</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1 ml</v>
+      </c>
+      <c r="F30" t="str">
+        <v>0,5 ml</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H30" t="str">
+        <v>RD-012</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Caso exitoso adicional 012.</v>
+      </c>
+      <c r="K30" t="str">
+        <v>INT-REAC-ADIC-012</v>
+      </c>
+      <c r="L30" t="str">
+        <v>ID-REAC-ADIC-012</v>
+      </c>
+      <c r="M30" t="str">
+        <v>BAR-REAC-ADIC-012</v>
+      </c>
+      <c r="N30" t="str">
+        <v>QR-REAC-ADIC-012</v>
+      </c>
+      <c r="O30" t="str">
+        <v>LOC-REAC-ADIC-012</v>
+      </c>
+      <c r="P30" t="str">
+        <v>TAG-REAC-ADIC-012</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>REAC-ADIC-013</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Reactivo de laboratorio de prueba 013</v>
+      </c>
+      <c r="C31" t="str">
+        <v>13 g</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H31" t="str">
+        <v>RD-013</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Caso exitoso adicional 013.</v>
+      </c>
+      <c r="K31" t="str">
+        <v>INT-REAC-ADIC-013</v>
+      </c>
+      <c r="L31" t="str">
+        <v>ID-REAC-ADIC-013</v>
+      </c>
+      <c r="M31" t="str">
+        <v>BAR-REAC-ADIC-013</v>
+      </c>
+      <c r="N31" t="str">
+        <v>QR-REAC-ADIC-013</v>
+      </c>
+      <c r="O31" t="str">
+        <v>LOC-REAC-ADIC-013</v>
+      </c>
+      <c r="P31" t="str">
+        <v>TAG-REAC-ADIC-013</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>REAC-ADIC-014</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Reactivo de laboratorio de prueba 014</v>
+      </c>
+      <c r="C32" t="str">
+        <v>14 g</v>
+      </c>
+      <c r="D32" t="str">
+        <v>14,5 g</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H32" t="str">
+        <v>RD-014</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Caso exitoso adicional 014.</v>
+      </c>
+      <c r="K32" t="str">
+        <v>INT-REAC-ADIC-014</v>
+      </c>
+      <c r="L32" t="str">
+        <v>ID-REAC-ADIC-014</v>
+      </c>
+      <c r="M32" t="str">
+        <v>BAR-REAC-ADIC-014</v>
+      </c>
+      <c r="N32" t="str">
+        <v>QR-REAC-ADIC-014</v>
+      </c>
+      <c r="O32" t="str">
+        <v>LOC-REAC-ADIC-014</v>
+      </c>
+      <c r="P32" t="str">
+        <v>TAG-REAC-ADIC-014</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>REAC-ADIC-015</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Reactivo de laboratorio de prueba 015</v>
+      </c>
+      <c r="C33" t="str">
+        <v>15 g</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>1 ml</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="H33" t="str">
+        <v>RD-015</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Caso exitoso adicional 015.</v>
+      </c>
+      <c r="K33" t="str">
+        <v>INT-REAC-ADIC-015</v>
+      </c>
+      <c r="L33" t="str">
+        <v>ID-REAC-ADIC-015</v>
+      </c>
+      <c r="M33" t="str">
+        <v>BAR-REAC-ADIC-015</v>
+      </c>
+      <c r="N33" t="str">
+        <v>QR-REAC-ADIC-015</v>
+      </c>
+      <c r="O33" t="str">
+        <v>LOC-REAC-ADIC-015</v>
+      </c>
+      <c r="P33" t="str">
+        <v>TAG-REAC-ADIC-015</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P33"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P33"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C36"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="78.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Fila en Inventario</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Resultado esperado</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Caso de prueba</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Reactivo válido con existencias en los cuatro balances y unidad.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Reactivo válido con existencia cero.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>4</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Reactivo válido sin saldos registrados.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Error intencional: falta la referencia del reactivo.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Error intencional: falta el nombre del reactivo.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>7</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Error intencional: cantidad de stock no numérica.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Error intencional: falta la unidad de medida.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Error intencional: cantidad negativa.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Error intencional: cantidad con más de tres decimales.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>11</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Error intencional: cantidad supera el máximo de dígitos enteros.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>12</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Error intencional: unidad de más de 50 caracteres.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>13</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Error intencional: referencia de más de 255 caracteres.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>14</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Error intencional: descripción de más de 1000 caracteres.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Error intencional: código QR duplicado.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>16</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Error intencional: observaciones de más de 2000 caracteres.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Saldos de stock y circulación separados por grado analítico.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>18</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Circulación cero válida con unidad.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Registro válido adicional 001.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Registro válido adicional 002.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Registro válido adicional 003.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Registro válido adicional 004.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Registro válido adicional 005.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Registro válido adicional 006.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Registro válido adicional 007.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Registro válido adicional 008.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Registro válido adicional 009.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Registro válido adicional 010.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Registro válido adicional 011.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Registro válido adicional 012.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Registro válido adicional 013.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Registro válido adicional 014.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Registro válido adicional 015.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Uso</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Carga únicamente la hoja Inventario; esta hoja documenta los resultados esperados.</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Nota</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Los casos fallidos son intencionales y sirven para verificar las validaciones del cargue.</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C36"/>
   </ignoredErrors>
 </worksheet>
 </file>